--- a/8-1 - BTS SIO - 2025 - Annexe 8-1 - Epreuve E5 - Tableau de synthèse.xlsx
+++ b/8-1 - BTS SIO - 2025 - Annexe 8-1 - Epreuve E5 - Tableau de synthèse.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brice\Desktop\ecole\Theo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brice\Documents\Nouveau dossier\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7FD9E0-5489-47C2-A04D-66EB5825F4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75D032F-DCBD-491D-8AF2-FB8B9E8CA54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -165,9 +165,6 @@
     <t>du 12/01/26 au 15/01/26</t>
   </si>
   <si>
-    <t>Déploiement automatique des imprimantes selon l'OU , via serveur d'impression grâce à une GPO</t>
-  </si>
-  <si>
     <t>Mise en conformité et automatisation de l'Active Directory</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
   </si>
   <si>
     <t>du 14/01/26 au 16/01/26</t>
-  </si>
-  <si>
-    <t>Demande de M. Lacombe pour sécuriser les données sensibles.</t>
   </si>
   <si>
     <t>Installation et configuration d'un serveur d'hypervision (Zabbix) d'équipement et appareils informatiques .</t>
@@ -815,6 +809,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -855,33 +876,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1226,56 +1220,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="53"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="60" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="55"/>
-      <c r="H3" s="61"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1287,22 +1281,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="57" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1325,8 +1319,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="43"/>
-      <c r="B7" s="49"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="26" t="s">
         <v>18</v>
       </c>
@@ -1382,16 +1376,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1486,7 +1480,9 @@
       <c r="B10" s="25">
         <v>45962</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="D10" s="19" t="s">
         <v>28</v>
       </c>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="24">
         <v>46023</v>
@@ -1541,7 +1537,9 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
+      <c r="G11" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="H11" s="15"/>
       <c r="I11"/>
       <c r="J11"/>
@@ -1592,7 +1590,9 @@
       <c r="F12" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="14"/>
+      <c r="G12" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="H12" s="15"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="14"/>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="29">
         <v>46113</v>
@@ -1745,7 +1745,9 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="G15" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="H15" s="15"/>
       <c r="I15"/>
       <c r="J15"/>
@@ -1785,7 +1787,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="29">
         <v>46143</v>
@@ -1795,7 +1797,9 @@
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="F16" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="G16" s="14"/>
       <c r="H16" s="15"/>
       <c r="I16"/>
@@ -1925,16 +1929,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="50"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1973,7 +1977,7 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="33">
         <v>45962</v>
@@ -2022,10 +2026,10 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>28</v>
@@ -2076,7 +2080,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>28</v>
@@ -2137,9 +2141,7 @@
         <v>28</v>
       </c>
       <c r="H23" s="15"/>
-      <c r="I23" s="34" t="s">
-        <v>35</v>
-      </c>
+      <c r="I23" s="34"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
@@ -2177,10 +2179,10 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -2228,10 +2230,10 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>38</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>39</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>28</v>
@@ -2241,9 +2243,7 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="15"/>
-      <c r="I25" s="35" t="s">
-        <v>40</v>
-      </c>
+      <c r="I25" s="35"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="29">
         <v>46082</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="14"/>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="38"/>
@@ -2433,16 +2433,16 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
+      <c r="A29" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="50"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2861,11 +2861,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
@@ -2873,6 +2868,11 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2883,14 +2883,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3005c40c-1001-4ba5-82d3-a83310342a20" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c9ae1c3b-2358-44e3-b744-611676976f7d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3155,21 +3153,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3005c40c-1001-4ba5-82d3-a83310342a20" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c9ae1c3b-2358-44e3-b744-611676976f7d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D68E777-1EC9-4011-84E2-3FE3FAFE47F9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA9F200-19EC-44AD-865B-E10E562E86EA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3005c40c-1001-4ba5-82d3-a83310342a20"/>
-    <ds:schemaRef ds:uri="c9ae1c3b-2358-44e3-b744-611676976f7d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3194,9 +3191,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA9F200-19EC-44AD-865B-E10E562E86EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D68E777-1EC9-4011-84E2-3FE3FAFE47F9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3005c40c-1001-4ba5-82d3-a83310342a20"/>
+    <ds:schemaRef ds:uri="c9ae1c3b-2358-44e3-b744-611676976f7d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>